--- a/tests/assets/golden/openpyxl/test_template_3_pivot_filled.xlsx
+++ b/tests/assets/golden/openpyxl/test_template_3_pivot_filled.xlsx
@@ -416,7 +416,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SalesData" displayName="SalesData" ref="A1:E7" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E7"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Region"/>
     <tableColumn id="2" name="Product"/>
